--- a/src/views/game/zlzq/cardList/jiaoshouCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/jiaoshouCard/z_level.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\jiaoshouCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11910" windowHeight="11745" firstSheet="2" activeTab="1"/>
+    <workbookView windowWidth="10080" windowHeight="10710" firstSheet="2" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
@@ -41,16 +46,16 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>旅行背包</t>
-  </si>
-  <si>
-    <t>天使琼浆</t>
-  </si>
-  <si>
-    <t>塔楼弓手</t>
-  </si>
-  <si>
-    <t>增援战线</t>
+    <t>圣殿斥候</t>
+  </si>
+  <si>
+    <t>圣殿卫士</t>
+  </si>
+  <si>
+    <t>民兵队长</t>
+  </si>
+  <si>
+    <t>圣殿弩手</t>
   </si>
   <si>
     <t>田园守望者</t>
@@ -62,13 +67,13 @@
     <t>蓝色卡等：</t>
   </si>
   <si>
-    <t>召集护卫</t>
-  </si>
-  <si>
-    <t>夺取阵地</t>
-  </si>
-  <si>
-    <t>惩戒天使</t>
+    <t>圣殿御卫</t>
+  </si>
+  <si>
+    <t>白袍主教</t>
+  </si>
+  <si>
+    <t>圣殿骑士</t>
   </si>
   <si>
     <t>紫色卡等：</t>
@@ -83,15 +88,15 @@
     <t>明日之音·露娜</t>
   </si>
   <si>
-    <t>符文·辉煌赞美诗</t>
-  </si>
-  <si>
     <t>帝国军魂·莱哈特</t>
   </si>
   <si>
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
+    <t>炫目天使·蕾娜</t>
+  </si>
+  <si>
     <t>钢铁统帅·雷蒙德</t>
   </si>
   <si>
@@ -104,49 +109,49 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>洞悉之眼</t>
+    <t>沉默术</t>
   </si>
   <si>
     <t>学仆-观测型</t>
   </si>
   <si>
-    <t>方尖魔碑</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>隐形术</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型</t>
-  </si>
-  <si>
-    <t>学仆-猛禽型</t>
-  </si>
-  <si>
-    <t>白首魔根</t>
-  </si>
-  <si>
-    <t>观星台大预言家1</t>
-  </si>
-  <si>
-    <t>观星台大预言家2</t>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>沉重否定3</t>
+  </si>
+  <si>
+    <t>虚化印记</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>克隆术2</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
+  </si>
+  <si>
+    <t>改造魔卷1</t>
+  </si>
+  <si>
+    <t>改造魔卷2</t>
+  </si>
+  <si>
+    <t>改造魔卷3</t>
   </si>
   <si>
     <t>米拉方舟</t>
   </si>
   <si>
+    <t>心灵操控</t>
+  </si>
+  <si>
     <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>No.9迪宁</t>
   </si>
   <si>
     <t>隐秘卡等：</t>
@@ -1188,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1199,7 +1204,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1207,10 +1212,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1221,7 +1226,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1232,7 +1237,7 @@
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1254,7 +1259,7 @@
       </c>
       <c r="C9" s="1">
         <f>AVERAGE(C2:C6)</f>
-        <v>21.6</v>
+        <v>23.8</v>
       </c>
       <c r="D9" s="2"/>
     </row>
@@ -1263,10 +1268,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1274,10 +1279,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1285,10 +1290,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1310,7 +1315,7 @@
       </c>
       <c r="C17" s="2">
         <f>AVERAGE(C12:C14)</f>
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1321,7 +1326,7 @@
         <v>3</v>
       </c>
       <c r="C20" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1332,7 +1337,7 @@
         <v>4</v>
       </c>
       <c r="C21" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1351,10 +1356,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1362,10 +1367,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1373,10 +1378,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1387,7 +1392,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1409,7 +1414,7 @@
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C20:C26)</f>
-        <v>20.4285714285714</v>
+        <v>23.2857142857143</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1421,14 +1426,14 @@
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C6,C12:C14,C20:C26)</f>
-        <v>20.9333333333333</v>
+        <v>23.6</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="C32 C9" formulaRange="1"/>
+    <ignoredError sqref="C9 C32" formulaRange="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1449,7 +1454,7 @@
         <v>24</v>
       </c>
       <c r="B1" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1">
         <v>12</v>
@@ -1463,7 +1468,7 @@
         <v>2</v>
       </c>
       <c r="C2" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1474,7 +1479,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1485,53 +1490,53 @@
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="1">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C1:C4)</f>
-        <v>18</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>20</v>
-      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C1:C6)</f>
+        <v>15.8333333333333</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
@@ -1541,7 +1546,7 @@
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1549,10 +1554,10 @@
         <v>31</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1574,7 +1579,7 @@
         <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1582,10 +1587,10 @@
         <v>34</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1593,7 +1598,7 @@
         <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C17" s="2">
         <v>12</v>
@@ -1611,9 +1616,15 @@
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="A19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="2">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -1621,26 +1632,20 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C10:C18)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="3">
-        <v>5</v>
-      </c>
-      <c r="C24" s="3">
-        <v>20</v>
+      <c r="C22" s="2">
+        <f>AVERAGE(C12:C19)</f>
+        <v>13.75</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1648,10 +1653,10 @@
         <v>38</v>
       </c>
       <c r="B25" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1672,8 +1677,8 @@
         <v>21</v>
       </c>
       <c r="C28" s="3">
-        <f>AVERAGE(C24:C25)</f>
-        <v>17</v>
+        <f>AVERAGE(C25:C25)</f>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1684,8 +1689,8 @@
         <v>39</v>
       </c>
       <c r="C31" s="4">
-        <f>AVERAGE(C1:C4,C10:C18,C24:C25)</f>
-        <v>17.2666666666667</v>
+        <f>AVERAGE(C1:C6,C12:C19,C25:C25)</f>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
